--- a/InputData/elec/SoESCaOMCbIC/Share of Electricity Sector Capital and OM Costs by ISIC Code.xlsx
+++ b/InputData/elec/SoESCaOMCbIC/Share of Electricity Sector Capital and OM Costs by ISIC Code.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\elec\SoESCaOMCbIC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\kjh_local\NEXTgroup_local\2025_local\2. EPS\업데이트 파일\eps-southkorea-3.3.1_2025update_v4.0.3\InputData\elec\SoESCaOMCbIC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F8CB7E-4F9B-4533-81A3-FD34044A8A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56960AD4-BC73-4312-9AD3-314C7FBC4630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="4" r:id="rId1"/>
@@ -22,9 +22,6 @@
     <sheet name="SoESCaOMCbIC-fixedOM" sheetId="6" r:id="rId7"/>
     <sheet name="SoESCaOMCbIC-variableOM" sheetId="5" r:id="rId8"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId9"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1591,32 +1588,32 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="0.000000000000000000%"/>
-    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="176" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="177" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="178" formatCode="0.0%"/>
+    <numFmt numFmtId="179" formatCode="0.0000"/>
+    <numFmt numFmtId="180" formatCode="0.000000000000000000%"/>
+    <numFmt numFmtId="181" formatCode="0.000"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1624,7 +1621,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1632,7 +1629,7 @@
       <b/>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1664,7 +1661,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1682,7 +1679,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1703,7 +1700,7 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1711,15 +1708,22 @@
       <i/>
       <sz val="11"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2167,14 +2171,14 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="3" applyBorder="1"/>
     <xf numFmtId="1" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -2186,10 +2190,10 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -2197,17 +2201,17 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="3" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="8" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2231,22 +2235,22 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2257,10 +2261,10 @@
     <xf numFmtId="1" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="3" applyBorder="1"/>
     <xf numFmtId="1" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -2268,7 +2272,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="3" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
@@ -2287,12 +2291,12 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2303,13 +2307,13 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="179" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2324,11 +2328,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2345,15 +2349,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="8" fillId="7" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="178" fontId="8" fillId="7" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="1" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="7" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2361,11 +2365,14 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2390,15 +2397,12 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Bad" xfId="2" builtinId="27"/>
-    <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="나쁨" xfId="2" builtinId="27"/>
+    <cellStyle name="백분율" xfId="1" builtinId="5"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="3" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2502,85 +2506,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="About"/>
-      <sheetName val="ATB Capital and O&amp;M Costs"/>
-      <sheetName val="ATB Weighted Offshore Wind"/>
-      <sheetName val="Soft Cost Calibration Data"/>
-      <sheetName val="MSW"/>
-      <sheetName val="Spur Line Costs"/>
-      <sheetName val="Capacity by Vintage"/>
-      <sheetName val="Existing O&amp;M Costs"/>
-      <sheetName val="BECCS"/>
-      <sheetName val="S&amp;L"/>
-      <sheetName val="Existing Plants"/>
-      <sheetName val="EIA 860 3.1"/>
-      <sheetName val="EIA 860 6A"/>
-      <sheetName val="EIA 860 6.2"/>
-      <sheetName val="Annual CAPEX Calcs"/>
-      <sheetName val="CCS Soft Costs"/>
-      <sheetName val="CCaMC-ACAPEXpUC"/>
-      <sheetName val="CCaMC-AFOaMCpUC"/>
-      <sheetName val="CCaMC-VOaMCpUC"/>
-      <sheetName val="CCaMC-BCCpUC"/>
-      <sheetName val="CCaMC-SLCCpUC"/>
-      <sheetName val="CCaMC-BSCpUC"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18">
-        <row r="2">
-          <cell r="EB2">
-            <v>7.1681929364874337</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="EB4">
-            <v>1.6607160940325494</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="EB10">
-            <v>4.2704128132265557</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="EB14">
-            <v>12.14376215122577</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2846,23 +2771,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:H42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="61.85546875" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" customWidth="1"/>
-    <col min="4" max="4" width="65.7109375" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" customWidth="1"/>
-    <col min="6" max="6" width="63.42578125" customWidth="1"/>
-    <col min="8" max="8" width="52.85546875" customWidth="1"/>
+    <col min="2" max="2" width="61.83203125" customWidth="1"/>
+    <col min="3" max="3" width="4.58203125" customWidth="1"/>
+    <col min="4" max="4" width="65.75" customWidth="1"/>
+    <col min="5" max="5" width="5.75" customWidth="1"/>
+    <col min="6" max="6" width="63.4140625" customWidth="1"/>
+    <col min="8" max="8" width="52.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="71" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" s="71" t="s">
         <v>214</v>
       </c>
@@ -2879,7 +2805,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>215</v>
       </c>
@@ -2893,7 +2819,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B5" s="79">
         <v>2022</v>
       </c>
@@ -2907,7 +2833,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>449</v>
       </c>
@@ -2921,7 +2847,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B7" s="65" t="s">
         <v>448</v>
       </c>
@@ -2935,7 +2861,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>450</v>
       </c>
@@ -2949,7 +2875,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B10" s="78" t="s">
         <v>327</v>
       </c>
@@ -2963,7 +2889,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>215</v>
       </c>
@@ -2977,7 +2903,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B12" s="79">
         <v>2019</v>
       </c>
@@ -2989,7 +2915,7 @@
       </c>
       <c r="H12" s="79"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>287</v>
       </c>
@@ -3000,7 +2926,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B14" s="65" t="s">
         <v>286</v>
       </c>
@@ -3012,7 +2938,7 @@
       </c>
       <c r="H14" s="65"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>288</v>
       </c>
@@ -3023,7 +2949,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B17" s="78" t="s">
         <v>223</v>
       </c>
@@ -3034,7 +2960,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
         <v>215</v>
       </c>
@@ -3045,7 +2971,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B19" s="79">
         <v>2016</v>
       </c>
@@ -3056,7 +2982,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="20" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" ht="34" x14ac:dyDescent="0.45">
       <c r="B20" s="107" t="s">
         <v>224</v>
       </c>
@@ -3069,7 +2995,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="21" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" ht="34" x14ac:dyDescent="0.45">
       <c r="B21" s="109" t="s">
         <v>114</v>
       </c>
@@ -3082,7 +3008,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
         <v>330</v>
       </c>
@@ -3093,7 +3019,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B24" s="78" t="s">
         <v>328</v>
       </c>
@@ -3104,7 +3030,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
         <v>215</v>
       </c>
@@ -3115,7 +3041,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B26" s="79">
         <v>2016</v>
       </c>
@@ -3126,7 +3052,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
         <v>329</v>
       </c>
@@ -3137,7 +3063,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B28" s="65" t="s">
         <v>255</v>
       </c>
@@ -3148,7 +3074,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
         <v>288</v>
       </c>
@@ -3159,42 +3085,43 @@
         <v>288</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A33" s="71" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>355</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="D14" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
@@ -3214,20 +3141,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:B43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="77.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.7109375" customWidth="1"/>
+    <col min="1" max="1" width="77.4140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.4140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.75" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.58203125" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="71" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="71" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="71" t="s">
         <v>194</v>
       </c>
@@ -3235,7 +3163,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>123</v>
       </c>
@@ -3243,7 +3171,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>429</v>
       </c>
@@ -3251,7 +3179,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>430</v>
       </c>
@@ -3259,7 +3187,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>447</v>
       </c>
@@ -3267,7 +3195,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>124</v>
       </c>
@@ -3275,7 +3203,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>125</v>
       </c>
@@ -3283,7 +3211,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>126</v>
       </c>
@@ -3291,7 +3219,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>127</v>
       </c>
@@ -3299,7 +3227,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>128</v>
       </c>
@@ -3307,7 +3235,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>129</v>
       </c>
@@ -3315,7 +3243,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>428</v>
       </c>
@@ -3323,7 +3251,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>427</v>
       </c>
@@ -3331,7 +3259,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>130</v>
       </c>
@@ -3339,7 +3267,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>440</v>
       </c>
@@ -3347,7 +3275,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>441</v>
       </c>
@@ -3355,7 +3283,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>442</v>
       </c>
@@ -3363,7 +3291,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>443</v>
       </c>
@@ -3371,7 +3299,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>131</v>
       </c>
@@ -3379,7 +3307,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>132</v>
       </c>
@@ -3387,7 +3315,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>133</v>
       </c>
@@ -3395,7 +3323,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>134</v>
       </c>
@@ -3403,7 +3331,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>135</v>
       </c>
@@ -3411,7 +3339,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>136</v>
       </c>
@@ -3419,7 +3347,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>137</v>
       </c>
@@ -3427,7 +3355,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>444</v>
       </c>
@@ -3435,7 +3363,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>445</v>
       </c>
@@ -3443,7 +3371,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>446</v>
       </c>
@@ -3451,7 +3379,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>138</v>
       </c>
@@ -3459,7 +3387,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>139</v>
       </c>
@@ -3467,7 +3395,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>140</v>
       </c>
@@ -3475,7 +3403,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>141</v>
       </c>
@@ -3483,7 +3411,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>142</v>
       </c>
@@ -3491,7 +3419,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>143</v>
       </c>
@@ -3499,7 +3427,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>144</v>
       </c>
@@ -3507,7 +3435,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>145</v>
       </c>
@@ -3515,7 +3443,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>146</v>
       </c>
@@ -3523,7 +3451,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>147</v>
       </c>
@@ -3531,7 +3459,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>148</v>
       </c>
@@ -3539,7 +3467,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>149</v>
       </c>
@@ -3547,7 +3475,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>150</v>
       </c>
@@ -3555,7 +3483,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>151</v>
       </c>
@@ -3563,7 +3491,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>152</v>
       </c>
@@ -3572,34 +3500,36 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:F381"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="65.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.140625" customWidth="1"/>
-    <col min="4" max="4" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="48.5703125" customWidth="1"/>
-    <col min="6" max="6" width="60.42578125" customWidth="1"/>
+    <col min="1" max="1" width="65.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.58203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.1640625" customWidth="1"/>
+    <col min="4" max="4" width="23.58203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="48.58203125" customWidth="1"/>
+    <col min="6" max="6" width="60.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="134" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="136"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="135" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="137"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -3619,7 +3549,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
@@ -3631,7 +3561,7 @@
       <c r="E3" s="21"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="s">
         <v>153</v>
       </c>
@@ -3654,7 +3584,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="7" t="s">
         <v>154</v>
       </c>
@@ -3677,7 +3607,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="7" t="s">
         <v>155</v>
       </c>
@@ -3700,7 +3630,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="7" t="s">
         <v>156</v>
       </c>
@@ -3723,7 +3653,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="7" t="s">
         <v>157</v>
       </c>
@@ -3746,7 +3676,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="7" t="s">
         <v>158</v>
       </c>
@@ -3769,7 +3699,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="7" t="s">
         <v>159</v>
       </c>
@@ -3792,7 +3722,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" s="7" t="s">
         <v>160</v>
       </c>
@@ -3815,7 +3745,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="7" t="s">
         <v>10</v>
       </c>
@@ -3838,7 +3768,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A13" s="57" t="s">
         <v>161</v>
       </c>
@@ -3861,7 +3791,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="88" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" s="88" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A14" s="11" t="s">
         <v>8</v>
       </c>
@@ -3871,7 +3801,7 @@
       <c r="E14" s="13"/>
       <c r="F14" s="14"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" s="7" t="s">
         <v>257</v>
       </c>
@@ -3894,7 +3824,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:6" s="87" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" s="87" customFormat="1" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A16" s="17" t="s">
         <v>258</v>
       </c>
@@ -3917,18 +3847,18 @@
         <v>114</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="130" t="s">
+    <row r="17" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="18" spans="1:6" ht="21.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A18" s="131" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="131"/>
-      <c r="C18" s="131"/>
-      <c r="D18" s="132"/>
-      <c r="E18" s="132"/>
-      <c r="F18" s="133"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B18" s="132"/>
+      <c r="C18" s="132"/>
+      <c r="D18" s="133"/>
+      <c r="E18" s="133"/>
+      <c r="F18" s="134"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19" s="92" t="s">
         <v>1</v>
       </c>
@@ -3948,7 +3878,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20" s="5" t="s">
         <v>6</v>
       </c>
@@ -3960,7 +3890,7 @@
       <c r="E20" s="21"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" s="20" t="s">
         <v>237</v>
       </c>
@@ -3970,7 +3900,7 @@
       <c r="E21" s="90"/>
       <c r="F21" s="56"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22" s="20" t="s">
         <v>259</v>
       </c>
@@ -3990,7 +3920,7 @@
       </c>
       <c r="F22" s="16"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23" s="20" t="s">
         <v>260</v>
       </c>
@@ -4010,7 +3940,7 @@
       </c>
       <c r="F23" s="16"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24" s="20" t="s">
         <v>261</v>
       </c>
@@ -4030,7 +3960,7 @@
       </c>
       <c r="F24" s="16"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A25" s="20" t="s">
         <v>262</v>
       </c>
@@ -4050,7 +3980,7 @@
       </c>
       <c r="F25" s="16"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A26" s="20" t="s">
         <v>263</v>
       </c>
@@ -4062,7 +3992,7 @@
       <c r="E26" s="90"/>
       <c r="F26" s="16"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27" s="20" t="s">
         <v>118</v>
       </c>
@@ -4072,7 +4002,7 @@
       <c r="E27" s="90"/>
       <c r="F27" s="16"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A28" s="20" t="s">
         <v>228</v>
       </c>
@@ -4082,7 +4012,7 @@
       <c r="E28" s="90"/>
       <c r="F28" s="16"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A29" s="20" t="s">
         <v>264</v>
       </c>
@@ -4102,7 +4032,7 @@
       </c>
       <c r="F29" s="16"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A30" s="20" t="s">
         <v>265</v>
       </c>
@@ -4122,7 +4052,7 @@
       </c>
       <c r="F30" s="16"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A31" s="20" t="s">
         <v>266</v>
       </c>
@@ -4142,7 +4072,7 @@
       </c>
       <c r="F31" s="16"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A32" s="20" t="s">
         <v>267</v>
       </c>
@@ -4162,7 +4092,7 @@
       </c>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A33" s="20" t="s">
         <v>268</v>
       </c>
@@ -4174,7 +4104,7 @@
       <c r="E33" s="90"/>
       <c r="F33" s="16"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A34" s="20" t="s">
         <v>231</v>
       </c>
@@ -4184,7 +4114,7 @@
       <c r="E34" s="90"/>
       <c r="F34" s="16"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A35" s="20" t="s">
         <v>269</v>
       </c>
@@ -4204,7 +4134,7 @@
       </c>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A36" s="20" t="s">
         <v>270</v>
       </c>
@@ -4224,7 +4154,7 @@
       </c>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A37" s="20" t="s">
         <v>236</v>
       </c>
@@ -4244,7 +4174,7 @@
       </c>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A38" s="20" t="s">
         <v>271</v>
       </c>
@@ -4264,7 +4194,7 @@
       </c>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A39" s="20" t="s">
         <v>272</v>
       </c>
@@ -4284,7 +4214,7 @@
       </c>
       <c r="F39" s="6"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A40" s="20" t="s">
         <v>273</v>
       </c>
@@ -4296,7 +4226,7 @@
       <c r="E40" s="21"/>
       <c r="F40" s="6"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A41" s="20" t="s">
         <v>274</v>
       </c>
@@ -4306,7 +4236,7 @@
       <c r="E41" s="21"/>
       <c r="F41" s="6"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A42" s="20" t="s">
         <v>275</v>
       </c>
@@ -4316,7 +4246,7 @@
       <c r="E42" s="21"/>
       <c r="F42" s="6"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A43" s="20" t="s">
         <v>276</v>
       </c>
@@ -4336,7 +4266,7 @@
       </c>
       <c r="F43" s="6"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A44" s="20" t="s">
         <v>277</v>
       </c>
@@ -4356,7 +4286,7 @@
       </c>
       <c r="F44" s="6"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A45" s="20" t="s">
         <v>278</v>
       </c>
@@ -4376,7 +4306,7 @@
       </c>
       <c r="F45" s="6"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A46" s="20" t="s">
         <v>279</v>
       </c>
@@ -4396,7 +4326,7 @@
       </c>
       <c r="F46" s="6"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A47" s="20" t="s">
         <v>280</v>
       </c>
@@ -4416,7 +4346,7 @@
       </c>
       <c r="F47" s="6"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A48" s="20" t="s">
         <v>281</v>
       </c>
@@ -4436,7 +4366,7 @@
       </c>
       <c r="F48" s="6"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A49" s="20" t="s">
         <v>282</v>
       </c>
@@ -4448,7 +4378,7 @@
       <c r="E49" s="21"/>
       <c r="F49" s="6"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A50" s="20" t="s">
         <v>283</v>
       </c>
@@ -4460,7 +4390,7 @@
       <c r="E50" s="21"/>
       <c r="F50" s="6"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A51" s="20" t="s">
         <v>284</v>
       </c>
@@ -4472,7 +4402,7 @@
       <c r="E51" s="21"/>
       <c r="F51" s="6"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A52" s="20" t="s">
         <v>285</v>
       </c>
@@ -4492,7 +4422,7 @@
       </c>
       <c r="F52" s="6"/>
     </row>
-    <row r="53" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A53" s="24" t="s">
         <v>11</v>
       </c>
@@ -4504,7 +4434,7 @@
       <c r="E53" s="25"/>
       <c r="F53" s="10"/>
     </row>
-    <row r="54" spans="1:6" s="88" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" s="88" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A54" s="11" t="s">
         <v>8</v>
       </c>
@@ -4514,7 +4444,7 @@
       <c r="E54" s="13"/>
       <c r="F54" s="14"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A55" s="20" t="s">
         <v>65</v>
       </c>
@@ -4524,7 +4454,7 @@
       <c r="E55" s="21"/>
       <c r="F55" s="6"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A56" s="20" t="s">
         <v>289</v>
       </c>
@@ -4534,7 +4464,7 @@
       <c r="E56" s="21"/>
       <c r="F56" s="6"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A57" s="20" t="s">
         <v>290</v>
       </c>
@@ -4554,7 +4484,7 @@
       </c>
       <c r="F57" s="6"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A58" s="20" t="s">
         <v>291</v>
       </c>
@@ -4574,7 +4504,7 @@
       </c>
       <c r="F58" s="6"/>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A59" s="20" t="s">
         <v>292</v>
       </c>
@@ -4594,7 +4524,7 @@
       </c>
       <c r="F59" s="6"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A60" s="20" t="s">
         <v>293</v>
       </c>
@@ -4606,7 +4536,7 @@
       <c r="E60" s="21"/>
       <c r="F60" s="6"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A61" s="20" t="s">
         <v>105</v>
       </c>
@@ -4616,7 +4546,7 @@
       <c r="E61" s="21"/>
       <c r="F61" s="6"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A62" s="20" t="s">
         <v>294</v>
       </c>
@@ -4636,7 +4566,7 @@
       </c>
       <c r="F62" s="6"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A63" s="20" t="s">
         <v>295</v>
       </c>
@@ -4656,7 +4586,7 @@
       </c>
       <c r="F63" s="6"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A64" s="20" t="s">
         <v>296</v>
       </c>
@@ -4676,7 +4606,7 @@
       </c>
       <c r="F64" s="6"/>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A65" s="20" t="s">
         <v>297</v>
       </c>
@@ -4696,7 +4626,7 @@
       </c>
       <c r="F65" s="6"/>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A66" s="20" t="s">
         <v>298</v>
       </c>
@@ -4716,7 +4646,7 @@
       </c>
       <c r="F66" s="6"/>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A67" s="20" t="s">
         <v>299</v>
       </c>
@@ -4736,7 +4666,7 @@
       </c>
       <c r="F67" s="6"/>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A68" s="20" t="s">
         <v>300</v>
       </c>
@@ -4756,7 +4686,7 @@
       </c>
       <c r="F68" s="6"/>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A69" s="20" t="s">
         <v>301</v>
       </c>
@@ -4776,7 +4706,7 @@
       </c>
       <c r="F69" s="6"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A70" s="20" t="s">
         <v>302</v>
       </c>
@@ -4788,7 +4718,7 @@
       <c r="E70" s="21"/>
       <c r="F70" s="6"/>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A71" s="20" t="s">
         <v>50</v>
       </c>
@@ -4808,7 +4738,7 @@
       </c>
       <c r="F71" s="6"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A72" s="20" t="s">
         <v>303</v>
       </c>
@@ -4820,7 +4750,7 @@
       <c r="E72" s="21"/>
       <c r="F72" s="6"/>
     </row>
-    <row r="73" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A73" s="24" t="s">
         <v>304</v>
       </c>
@@ -4832,18 +4762,18 @@
       <c r="E73" s="25"/>
       <c r="F73" s="10"/>
     </row>
-    <row r="74" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="75" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A75" s="134" t="s">
+    <row r="74" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="75" spans="1:6" ht="21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" s="135" t="s">
         <v>12</v>
       </c>
-      <c r="B75" s="135"/>
-      <c r="C75" s="135"/>
-      <c r="D75" s="137"/>
-      <c r="E75" s="137"/>
-      <c r="F75" s="136"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B75" s="136"/>
+      <c r="C75" s="136"/>
+      <c r="D75" s="138"/>
+      <c r="E75" s="138"/>
+      <c r="F75" s="137"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A76" s="1" t="s">
         <v>1</v>
       </c>
@@ -4863,7 +4793,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A77" s="5" t="s">
         <v>6</v>
       </c>
@@ -4871,7 +4801,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A78" s="7" t="s">
         <v>14</v>
       </c>
@@ -4882,7 +4812,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A79" s="7" t="s">
         <v>16</v>
       </c>
@@ -4904,7 +4834,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A80" s="7" t="s">
         <v>17</v>
       </c>
@@ -4926,7 +4856,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A81" s="7" t="s">
         <v>18</v>
       </c>
@@ -4948,7 +4878,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A82" s="30" t="s">
         <v>19</v>
       </c>
@@ -4963,7 +4893,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A83" s="7" t="s">
         <v>20</v>
       </c>
@@ -4975,7 +4905,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A84" s="7" t="s">
         <v>21</v>
       </c>
@@ -4997,7 +4927,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A85" s="7" t="s">
         <v>22</v>
       </c>
@@ -5019,7 +4949,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A86" s="30" t="s">
         <v>23</v>
       </c>
@@ -5034,7 +4964,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A87" s="30" t="s">
         <v>24</v>
       </c>
@@ -5049,7 +4979,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A88" s="5" t="s">
         <v>25</v>
       </c>
@@ -5061,7 +4991,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A89" s="7" t="s">
         <v>26</v>
       </c>
@@ -5083,7 +5013,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A90" s="7" t="s">
         <v>27</v>
       </c>
@@ -5105,7 +5035,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A91" s="7" t="s">
         <v>28</v>
       </c>
@@ -5127,7 +5057,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A92" s="7" t="s">
         <v>29</v>
       </c>
@@ -5149,7 +5079,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A93" s="7" t="s">
         <v>30</v>
       </c>
@@ -5171,7 +5101,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A94" s="7" t="s">
         <v>31</v>
       </c>
@@ -5193,7 +5123,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A95" s="7" t="s">
         <v>32</v>
       </c>
@@ -5215,7 +5145,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A96" s="7" t="s">
         <v>33</v>
       </c>
@@ -5237,7 +5167,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A97" s="30" t="s">
         <v>34</v>
       </c>
@@ -5250,7 +5180,7 @@
       <c r="E97" s="73"/>
       <c r="F97" s="16"/>
     </row>
-    <row r="98" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A98" s="31" t="s">
         <v>35</v>
       </c>
@@ -5263,7 +5193,7 @@
       <c r="E98" s="34"/>
       <c r="F98" s="35"/>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A99" s="11" t="s">
         <v>8</v>
       </c>
@@ -5273,7 +5203,7 @@
       <c r="E99" s="37"/>
       <c r="F99" s="14"/>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A100" s="38" t="s">
         <v>20</v>
       </c>
@@ -5295,7 +5225,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A101" s="38" t="s">
         <v>36</v>
       </c>
@@ -5317,7 +5247,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A102" s="38" t="s">
         <v>37</v>
       </c>
@@ -5339,7 +5269,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A103" s="40" t="s">
         <v>35</v>
       </c>
@@ -5352,7 +5282,7 @@
       <c r="E103" s="43"/>
       <c r="F103" s="10"/>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A104" s="11" t="s">
         <v>38</v>
       </c>
@@ -5362,7 +5292,7 @@
       <c r="E104" s="37"/>
       <c r="F104" s="14"/>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A105" s="38" t="s">
         <v>39</v>
       </c>
@@ -5384,7 +5314,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A106" s="38" t="s">
         <v>40</v>
       </c>
@@ -5406,7 +5336,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A107" s="38" t="s">
         <v>29</v>
       </c>
@@ -5428,7 +5358,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A108" s="40" t="s">
         <v>35</v>
       </c>
@@ -5441,18 +5371,18 @@
       <c r="E108" s="43"/>
       <c r="F108" s="10"/>
     </row>
-    <row r="109" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="110" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A110" s="134" t="s">
+    <row r="109" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="110" spans="1:6" ht="21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A110" s="135" t="s">
         <v>41</v>
       </c>
-      <c r="B110" s="135"/>
-      <c r="C110" s="135"/>
-      <c r="D110" s="137"/>
-      <c r="E110" s="137"/>
-      <c r="F110" s="136"/>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B110" s="136"/>
+      <c r="C110" s="136"/>
+      <c r="D110" s="138"/>
+      <c r="E110" s="138"/>
+      <c r="F110" s="137"/>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A111" s="1" t="s">
         <v>1</v>
       </c>
@@ -5472,7 +5402,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A112" s="5" t="s">
         <v>6</v>
       </c>
@@ -5484,12 +5414,12 @@
       <c r="E112" s="3"/>
       <c r="F112" s="16"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A113" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A114" s="7" t="s">
         <v>16</v>
       </c>
@@ -5511,7 +5441,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A115" s="7" t="s">
         <v>17</v>
       </c>
@@ -5533,7 +5463,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A116" s="7" t="s">
         <v>18</v>
       </c>
@@ -5555,7 +5485,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A117" s="7" t="s">
         <v>43</v>
       </c>
@@ -5569,7 +5499,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A118" s="7" t="s">
         <v>44</v>
       </c>
@@ -5581,7 +5511,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A119" s="7" t="s">
         <v>21</v>
       </c>
@@ -5603,7 +5533,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A120" s="7" t="s">
         <v>45</v>
       </c>
@@ -5625,7 +5555,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A121" s="7" t="s">
         <v>46</v>
       </c>
@@ -5647,7 +5577,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A122" s="7" t="s">
         <v>43</v>
       </c>
@@ -5661,7 +5591,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A123" s="7" t="s">
         <v>24</v>
       </c>
@@ -5675,7 +5605,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A124" s="5" t="s">
         <v>25</v>
       </c>
@@ -5687,7 +5617,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A125" s="7" t="s">
         <v>47</v>
       </c>
@@ -5709,7 +5639,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A126" s="7" t="s">
         <v>27</v>
       </c>
@@ -5731,7 +5661,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A127" s="7" t="s">
         <v>28</v>
       </c>
@@ -5753,7 +5683,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A128" s="7" t="s">
         <v>48</v>
       </c>
@@ -5775,7 +5705,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A129" s="7" t="s">
         <v>30</v>
       </c>
@@ -5797,7 +5727,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A130" s="7" t="s">
         <v>33</v>
       </c>
@@ -5819,7 +5749,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A131" s="7" t="s">
         <v>34</v>
       </c>
@@ -5831,7 +5761,7 @@
       <c r="E131" s="73"/>
       <c r="F131" s="16"/>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A132" s="5" t="s">
         <v>49</v>
       </c>
@@ -5845,7 +5775,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="133" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A133" s="47" t="s">
         <v>50</v>
       </c>
@@ -5860,7 +5790,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A134" s="11" t="s">
         <v>8</v>
       </c>
@@ -5872,7 +5802,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A135" s="38" t="s">
         <v>20</v>
       </c>
@@ -5894,7 +5824,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A136" s="38" t="s">
         <v>36</v>
       </c>
@@ -5916,7 +5846,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A137" s="38" t="s">
         <v>37</v>
       </c>
@@ -5938,7 +5868,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="138" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A138" s="40" t="s">
         <v>35</v>
       </c>
@@ -5953,7 +5883,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A139" s="11" t="s">
         <v>38</v>
       </c>
@@ -5963,7 +5893,7 @@
       <c r="E139" s="37"/>
       <c r="F139" s="14"/>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A140" s="38" t="s">
         <v>51</v>
       </c>
@@ -5985,7 +5915,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A141" s="38" t="s">
         <v>40</v>
       </c>
@@ -6007,7 +5937,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A142" s="38" t="s">
         <v>29</v>
       </c>
@@ -6029,7 +5959,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="143" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A143" s="40" t="s">
         <v>35</v>
       </c>
@@ -6042,18 +5972,18 @@
       <c r="E143" s="26"/>
       <c r="F143" s="10"/>
     </row>
-    <row r="144" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="145" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A145" s="130" t="s">
+    <row r="144" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="145" spans="1:6" ht="21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A145" s="131" t="s">
         <v>52</v>
       </c>
-      <c r="B145" s="131"/>
-      <c r="C145" s="131"/>
-      <c r="D145" s="132"/>
-      <c r="E145" s="132"/>
-      <c r="F145" s="133"/>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B145" s="132"/>
+      <c r="C145" s="132"/>
+      <c r="D145" s="133"/>
+      <c r="E145" s="133"/>
+      <c r="F145" s="134"/>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A146" s="1" t="s">
         <v>1</v>
       </c>
@@ -6073,7 +6003,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A147" s="5" t="s">
         <v>6</v>
       </c>
@@ -6085,7 +6015,7 @@
       <c r="E147" s="3"/>
       <c r="F147" s="16"/>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A148" s="7" t="s">
         <v>53</v>
       </c>
@@ -6095,7 +6025,7 @@
       <c r="E148" s="22"/>
       <c r="F148" s="6"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A149" s="7" t="s">
         <v>54</v>
       </c>
@@ -6114,7 +6044,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A150" s="7" t="s">
         <v>57</v>
       </c>
@@ -6136,7 +6066,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A151" s="7" t="s">
         <v>58</v>
       </c>
@@ -6158,7 +6088,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A152" s="7" t="s">
         <v>59</v>
       </c>
@@ -6180,7 +6110,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A153" s="7" t="s">
         <v>60</v>
       </c>
@@ -6202,7 +6132,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A154" s="7" t="s">
         <v>61</v>
       </c>
@@ -6224,7 +6154,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A155" s="7" t="s">
         <v>62</v>
       </c>
@@ -6246,7 +6176,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A156" s="7" t="s">
         <v>63</v>
       </c>
@@ -6268,7 +6198,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A157" s="7" t="s">
         <v>64</v>
       </c>
@@ -6290,7 +6220,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A158" s="57" t="s">
         <v>11</v>
       </c>
@@ -6304,7 +6234,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A159" s="11" t="s">
         <v>8</v>
       </c>
@@ -6314,7 +6244,7 @@
       <c r="E159" s="60"/>
       <c r="F159" s="14"/>
     </row>
-    <row r="160" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A160" s="57" t="s">
         <v>65</v>
       </c>
@@ -6336,7 +6266,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A161" s="11" t="s">
         <v>38</v>
       </c>
@@ -6346,7 +6276,7 @@
       <c r="E161" s="60"/>
       <c r="F161" s="14"/>
     </row>
-    <row r="162" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A162" s="24" t="s">
         <v>68</v>
       </c>
@@ -6368,18 +6298,18 @@
         <v>70</v>
       </c>
     </row>
-    <row r="163" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="164" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A164" s="130" t="s">
+    <row r="163" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="164" spans="1:6" ht="21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A164" s="131" t="s">
         <v>71</v>
       </c>
-      <c r="B164" s="131"/>
-      <c r="C164" s="131"/>
-      <c r="D164" s="132"/>
-      <c r="E164" s="132"/>
-      <c r="F164" s="133"/>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B164" s="132"/>
+      <c r="C164" s="132"/>
+      <c r="D164" s="133"/>
+      <c r="E164" s="133"/>
+      <c r="F164" s="134"/>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A165" s="1" t="s">
         <v>1</v>
       </c>
@@ -6399,7 +6329,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A166" s="5" t="s">
         <v>6</v>
       </c>
@@ -6411,7 +6341,7 @@
       <c r="E166" s="3"/>
       <c r="F166" s="16"/>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A167" s="62" t="s">
         <v>72</v>
       </c>
@@ -6422,7 +6352,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A168" s="7" t="s">
         <v>74</v>
       </c>
@@ -6444,7 +6374,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A169" s="7" t="s">
         <v>75</v>
       </c>
@@ -6466,7 +6396,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A170" s="7" t="s">
         <v>76</v>
       </c>
@@ -6480,7 +6410,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A171" s="7" t="s">
         <v>77</v>
       </c>
@@ -6492,7 +6422,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A172" s="7" t="s">
         <v>78</v>
       </c>
@@ -6514,7 +6444,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A173" s="7" t="s">
         <v>79</v>
       </c>
@@ -6528,7 +6458,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A174" s="7" t="s">
         <v>80</v>
       </c>
@@ -6540,7 +6470,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A175" s="7" t="s">
         <v>81</v>
       </c>
@@ -6562,7 +6492,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A176" s="7" t="s">
         <v>82</v>
       </c>
@@ -6584,7 +6514,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A177" s="7" t="s">
         <v>83</v>
       </c>
@@ -6606,7 +6536,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A178" s="7" t="s">
         <v>84</v>
       </c>
@@ -6628,7 +6558,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A179" s="7" t="s">
         <v>85</v>
       </c>
@@ -6650,7 +6580,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A180" s="7" t="s">
         <v>86</v>
       </c>
@@ -6672,7 +6602,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A181" s="7" t="s">
         <v>87</v>
       </c>
@@ -6694,7 +6624,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A182" s="7" t="s">
         <v>88</v>
       </c>
@@ -6708,7 +6638,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A183" s="7" t="s">
         <v>89</v>
       </c>
@@ -6720,7 +6650,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A184" s="7" t="s">
         <v>78</v>
       </c>
@@ -6742,7 +6672,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A185" s="7" t="s">
         <v>90</v>
       </c>
@@ -6764,7 +6694,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A186" s="7" t="s">
         <v>91</v>
       </c>
@@ -6786,7 +6716,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A187" s="7" t="s">
         <v>92</v>
       </c>
@@ -6808,7 +6738,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A188" s="7" t="s">
         <v>93</v>
       </c>
@@ -6830,7 +6760,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A189" s="7" t="s">
         <v>94</v>
       </c>
@@ -6852,7 +6782,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A190" s="7" t="s">
         <v>95</v>
       </c>
@@ -6874,7 +6804,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A191" s="7" t="s">
         <v>96</v>
       </c>
@@ -6896,7 +6826,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A192" s="7" t="s">
         <v>97</v>
       </c>
@@ -6910,7 +6840,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A193" s="7" t="s">
         <v>25</v>
       </c>
@@ -6922,7 +6852,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A194" s="7" t="s">
         <v>98</v>
       </c>
@@ -6944,7 +6874,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A195" s="7" t="s">
         <v>99</v>
       </c>
@@ -6966,7 +6896,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A196" s="7" t="s">
         <v>100</v>
       </c>
@@ -6988,7 +6918,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A197" s="7" t="s">
         <v>101</v>
       </c>
@@ -7010,7 +6940,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A198" s="7" t="s">
         <v>102</v>
       </c>
@@ -7032,7 +6962,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A199" s="7" t="s">
         <v>34</v>
       </c>
@@ -7046,7 +6976,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A200" s="7" t="s">
         <v>103</v>
       </c>
@@ -7060,7 +6990,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A201" s="7" t="s">
         <v>50</v>
       </c>
@@ -7074,7 +7004,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="202" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A202" s="57" t="s">
         <v>11</v>
       </c>
@@ -7088,7 +7018,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A203" s="11" t="s">
         <v>8</v>
       </c>
@@ -7100,7 +7030,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A204" s="7" t="s">
         <v>104</v>
       </c>
@@ -7122,7 +7052,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A205" s="7" t="s">
         <v>105</v>
       </c>
@@ -7134,7 +7064,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A206" s="7" t="s">
         <v>106</v>
       </c>
@@ -7156,7 +7086,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A207" s="7" t="s">
         <v>101</v>
       </c>
@@ -7178,7 +7108,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A208" s="7" t="s">
         <v>107</v>
       </c>
@@ -7200,7 +7130,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A209" s="7" t="s">
         <v>108</v>
       </c>
@@ -7222,7 +7152,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A210" s="7" t="s">
         <v>109</v>
       </c>
@@ -7244,7 +7174,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A211" s="7" t="s">
         <v>110</v>
       </c>
@@ -7266,7 +7196,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A212" s="7" t="s">
         <v>111</v>
       </c>
@@ -7280,7 +7210,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A213" s="7" t="s">
         <v>103</v>
       </c>
@@ -7294,7 +7224,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A214" s="7" t="s">
         <v>50</v>
       </c>
@@ -7308,7 +7238,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="215" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A215" s="57" t="s">
         <v>112</v>
       </c>
@@ -7322,7 +7252,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A216" s="11" t="s">
         <v>38</v>
       </c>
@@ -7332,7 +7262,7 @@
       <c r="E216" s="60"/>
       <c r="F216" s="14"/>
     </row>
-    <row r="217" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A217" s="17" t="s">
         <v>308</v>
       </c>
@@ -7354,18 +7284,18 @@
         <v>309</v>
       </c>
     </row>
-    <row r="218" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="219" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A219" s="130" t="s">
+    <row r="218" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="219" spans="1:6" ht="21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A219" s="131" t="s">
         <v>226</v>
       </c>
-      <c r="B219" s="131"/>
-      <c r="C219" s="131"/>
-      <c r="D219" s="132"/>
-      <c r="E219" s="132"/>
-      <c r="F219" s="133"/>
-    </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B219" s="132"/>
+      <c r="C219" s="132"/>
+      <c r="D219" s="133"/>
+      <c r="E219" s="133"/>
+      <c r="F219" s="134"/>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A220" s="1" t="s">
         <v>1</v>
       </c>
@@ -7385,7 +7315,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A221" s="5" t="s">
         <v>6</v>
       </c>
@@ -7397,7 +7327,7 @@
       <c r="E221" s="3"/>
       <c r="F221" s="16"/>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A222" s="20" t="s">
         <v>113</v>
       </c>
@@ -7419,7 +7349,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A223" s="20" t="s">
         <v>115</v>
       </c>
@@ -7441,7 +7371,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A224" s="20" t="s">
         <v>116</v>
       </c>
@@ -7463,7 +7393,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A225" s="20" t="s">
         <v>117</v>
       </c>
@@ -7485,7 +7415,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A226" s="20" t="s">
         <v>118</v>
       </c>
@@ -7507,7 +7437,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="227" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A227" s="67" t="s">
         <v>119</v>
       </c>
@@ -7529,7 +7459,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A228" s="11" t="s">
         <v>8</v>
       </c>
@@ -7539,7 +7469,7 @@
       <c r="E228" s="60"/>
       <c r="F228" s="52"/>
     </row>
-    <row r="229" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A229" s="24" t="s">
         <v>65</v>
       </c>
@@ -7561,7 +7491,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A230" s="11" t="s">
         <v>38</v>
       </c>
@@ -7571,7 +7501,7 @@
       <c r="E230" s="60"/>
       <c r="F230" s="14"/>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A231" s="7" t="s">
         <v>120</v>
       </c>
@@ -7593,7 +7523,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A232" s="7" t="s">
         <v>121</v>
       </c>
@@ -7615,7 +7545,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="233" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A233" s="17" t="s">
         <v>122</v>
       </c>
@@ -7637,18 +7567,18 @@
         <v>114</v>
       </c>
     </row>
-    <row r="234" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="235" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A235" s="130" t="s">
+    <row r="234" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="235" spans="1:6" ht="21" x14ac:dyDescent="0.55000000000000004">
+      <c r="A235" s="131" t="s">
         <v>227</v>
       </c>
-      <c r="B235" s="131"/>
-      <c r="C235" s="131"/>
-      <c r="D235" s="132"/>
-      <c r="E235" s="132"/>
-      <c r="F235" s="133"/>
-    </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B235" s="132"/>
+      <c r="C235" s="132"/>
+      <c r="D235" s="133"/>
+      <c r="E235" s="133"/>
+      <c r="F235" s="134"/>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A236" s="1" t="s">
         <v>1</v>
       </c>
@@ -7668,7 +7598,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A237" s="5" t="s">
         <v>6</v>
       </c>
@@ -7680,7 +7610,7 @@
       <c r="E237" s="2"/>
       <c r="F237" s="16"/>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A238" s="83" t="s">
         <v>228</v>
       </c>
@@ -7690,7 +7620,7 @@
       <c r="E238" s="21"/>
       <c r="F238" s="56"/>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A239" s="83" t="s">
         <v>229</v>
       </c>
@@ -7712,7 +7642,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A240" s="83" t="s">
         <v>230</v>
       </c>
@@ -7724,7 +7654,7 @@
       <c r="E240" s="21"/>
       <c r="F240" s="16"/>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A241" s="83" t="s">
         <v>231</v>
       </c>
@@ -7734,7 +7664,7 @@
       <c r="E241" s="21"/>
       <c r="F241" s="16"/>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A242" s="83" t="s">
         <v>232</v>
       </c>
@@ -7756,7 +7686,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A243" s="83" t="s">
         <v>233</v>
       </c>
@@ -7778,7 +7708,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A244" s="38" t="s">
         <v>234</v>
       </c>
@@ -7800,7 +7730,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A245" s="83" t="s">
         <v>235</v>
       </c>
@@ -7822,7 +7752,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A246" s="38" t="s">
         <v>236</v>
       </c>
@@ -7844,7 +7774,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A247" s="7" t="s">
         <v>230</v>
       </c>
@@ -7856,7 +7786,7 @@
       <c r="E247" s="21"/>
       <c r="F247" s="16"/>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A248" s="7" t="s">
         <v>76</v>
       </c>
@@ -7868,7 +7798,7 @@
       <c r="E248" s="21"/>
       <c r="F248" s="16"/>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A249" s="7" t="s">
         <v>237</v>
       </c>
@@ -7878,7 +7808,7 @@
       <c r="E249" s="21"/>
       <c r="F249" s="16"/>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A250" s="83" t="s">
         <v>238</v>
       </c>
@@ -7900,7 +7830,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A251" s="83" t="s">
         <v>239</v>
       </c>
@@ -7922,7 +7852,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A252" s="83" t="s">
         <v>240</v>
       </c>
@@ -7944,7 +7874,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A253" s="83" t="s">
         <v>241</v>
       </c>
@@ -7966,7 +7896,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A254" s="83" t="s">
         <v>242</v>
       </c>
@@ -7988,7 +7918,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A255" s="83" t="s">
         <v>243</v>
       </c>
@@ -8010,7 +7940,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A256" s="83" t="s">
         <v>244</v>
       </c>
@@ -8032,7 +7962,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A257" s="83" t="s">
         <v>245</v>
       </c>
@@ -8054,7 +7984,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A258" s="83" t="s">
         <v>246</v>
       </c>
@@ -8076,7 +8006,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A259" s="83" t="s">
         <v>247</v>
       </c>
@@ -8098,7 +8028,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A260" s="83" t="s">
         <v>248</v>
       </c>
@@ -8120,7 +8050,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A261" s="83" t="s">
         <v>249</v>
       </c>
@@ -8142,7 +8072,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A262" s="83" t="s">
         <v>250</v>
       </c>
@@ -8164,7 +8094,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A263" s="83" t="s">
         <v>76</v>
       </c>
@@ -8176,7 +8106,7 @@
       <c r="E263" s="21"/>
       <c r="F263" s="6"/>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A264" s="83" t="s">
         <v>25</v>
       </c>
@@ -8186,7 +8116,7 @@
       <c r="E264" s="21"/>
       <c r="F264" s="6"/>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A265" s="83" t="s">
         <v>251</v>
       </c>
@@ -8208,7 +8138,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A266" s="83" t="s">
         <v>252</v>
       </c>
@@ -8230,7 +8160,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A267" s="83" t="s">
         <v>253</v>
       </c>
@@ -8252,7 +8182,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A268" s="83" t="s">
         <v>76</v>
       </c>
@@ -8264,7 +8194,7 @@
       <c r="E268" s="21"/>
       <c r="F268" s="6"/>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A269" s="83" t="s">
         <v>103</v>
       </c>
@@ -8276,7 +8206,7 @@
       <c r="E269" s="21"/>
       <c r="F269" s="6"/>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A270" s="83" t="s">
         <v>254</v>
       </c>
@@ -8286,7 +8216,7 @@
       <c r="E270" s="21"/>
       <c r="F270" s="6"/>
     </row>
-    <row r="271" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A271" s="85" t="s">
         <v>11</v>
       </c>
@@ -8296,7 +8226,7 @@
       <c r="E271" s="25"/>
       <c r="F271" s="10"/>
     </row>
-    <row r="272" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A272" s="96" t="s">
         <v>8</v>
       </c>
@@ -8306,7 +8236,7 @@
       <c r="E272" s="97"/>
       <c r="F272" s="98"/>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A273" s="99" t="s">
         <v>289</v>
       </c>
@@ -8316,7 +8246,7 @@
       <c r="E273" s="60"/>
       <c r="F273" s="14"/>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A274" s="83" t="s">
         <v>315</v>
       </c>
@@ -8338,7 +8268,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A275" s="83" t="s">
         <v>291</v>
       </c>
@@ -8360,7 +8290,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A276" s="83" t="s">
         <v>316</v>
       </c>
@@ -8382,7 +8312,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A277" s="83" t="s">
         <v>317</v>
       </c>
@@ -8404,7 +8334,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A278" s="83" t="s">
         <v>314</v>
       </c>
@@ -8416,7 +8346,7 @@
       <c r="E278" s="21"/>
       <c r="F278" s="6"/>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A279" s="83" t="s">
         <v>105</v>
       </c>
@@ -8426,7 +8356,7 @@
       <c r="E279" s="21"/>
       <c r="F279" s="6"/>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A280" s="83" t="s">
         <v>318</v>
       </c>
@@ -8446,7 +8376,7 @@
       </c>
       <c r="F280" s="6"/>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A281" s="83" t="s">
         <v>319</v>
       </c>
@@ -8468,7 +8398,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A282" s="83" t="s">
         <v>320</v>
       </c>
@@ -8490,7 +8420,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A283" s="83" t="s">
         <v>297</v>
       </c>
@@ -8512,7 +8442,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A284" s="83" t="s">
         <v>299</v>
       </c>
@@ -8534,7 +8464,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A285" s="83" t="s">
         <v>321</v>
       </c>
@@ -8556,7 +8486,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A286" s="83" t="s">
         <v>322</v>
       </c>
@@ -8578,7 +8508,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A287" s="83" t="s">
         <v>302</v>
       </c>
@@ -8590,7 +8520,7 @@
       <c r="E287" s="21"/>
       <c r="F287" s="6"/>
     </row>
-    <row r="288" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A288" s="85" t="s">
         <v>11</v>
       </c>
@@ -8602,17 +8532,17 @@
       <c r="E288" s="25"/>
       <c r="F288" s="10"/>
     </row>
-    <row r="289" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A289" s="130" t="s">
+    <row r="289" spans="1:6" ht="21.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A289" s="131" t="s">
         <v>337</v>
       </c>
-      <c r="B289" s="131"/>
-      <c r="C289" s="131"/>
-      <c r="D289" s="132"/>
-      <c r="E289" s="132"/>
-      <c r="F289" s="133"/>
-    </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B289" s="132"/>
+      <c r="C289" s="132"/>
+      <c r="D289" s="133"/>
+      <c r="E289" s="133"/>
+      <c r="F289" s="134"/>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A290" s="92" t="s">
         <v>1</v>
       </c>
@@ -8632,7 +8562,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A291" s="5" t="s">
         <v>6</v>
       </c>
@@ -8644,7 +8574,7 @@
       <c r="E291" s="2"/>
       <c r="F291" s="16"/>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A292" s="86" t="s">
         <v>338</v>
       </c>
@@ -8654,7 +8584,7 @@
       <c r="E292" s="21"/>
       <c r="F292" s="6"/>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A293" s="83" t="s">
         <v>339</v>
       </c>
@@ -8676,7 +8606,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A294" s="83" t="s">
         <v>340</v>
       </c>
@@ -8698,7 +8628,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A295" s="83" t="s">
         <v>341</v>
       </c>
@@ -8720,7 +8650,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A296" s="83" t="s">
         <v>342</v>
       </c>
@@ -8742,7 +8672,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A297" s="83" t="s">
         <v>343</v>
       </c>
@@ -8764,7 +8694,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A298" s="83" t="s">
         <v>344</v>
       </c>
@@ -8786,7 +8716,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A299" s="83" t="s">
         <v>345</v>
       </c>
@@ -8808,7 +8738,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A300" s="83" t="s">
         <v>346</v>
       </c>
@@ -8830,7 +8760,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A301" s="83" t="s">
         <v>347</v>
       </c>
@@ -8852,7 +8782,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A302" s="86" t="s">
         <v>348</v>
       </c>
@@ -8862,7 +8792,7 @@
       <c r="E302" s="21"/>
       <c r="F302" s="6"/>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A303" s="83" t="s">
         <v>349</v>
       </c>
@@ -8884,7 +8814,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A304" s="83" t="s">
         <v>350</v>
       </c>
@@ -8906,7 +8836,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A305" s="83" t="s">
         <v>351</v>
       </c>
@@ -8928,7 +8858,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="306" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A306" s="84" t="s">
         <v>352</v>
       </c>
@@ -8950,7 +8880,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A307" s="11" t="s">
         <v>8</v>
       </c>
@@ -8960,7 +8890,7 @@
       <c r="E307" s="60"/>
       <c r="F307" s="14"/>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A308" s="83" t="s">
         <v>65</v>
       </c>
@@ -8982,7 +8912,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A309" s="83" t="s">
         <v>358</v>
       </c>
@@ -9004,7 +8934,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A310" s="83" t="s">
         <v>359</v>
       </c>
@@ -9026,7 +8956,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="311" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A311" s="84" t="s">
         <v>360</v>
       </c>
@@ -9048,7 +8978,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A312" s="11" t="s">
         <v>38</v>
       </c>
@@ -9058,7 +8988,7 @@
       <c r="E312" s="60"/>
       <c r="F312" s="14"/>
     </row>
-    <row r="313" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:6" ht="27.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A313" s="106" t="s">
         <v>356</v>
       </c>
@@ -9080,22 +9010,22 @@
         <v>70</v>
       </c>
     </row>
-    <row r="314" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B314" s="81"/>
       <c r="C314" s="80"/>
       <c r="D314" s="101"/>
     </row>
-    <row r="315" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A315" s="130" t="s">
+    <row r="315" spans="1:6" ht="21.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A315" s="131" t="s">
         <v>365</v>
       </c>
-      <c r="B315" s="131"/>
-      <c r="C315" s="131"/>
-      <c r="D315" s="132"/>
-      <c r="E315" s="132"/>
-      <c r="F315" s="133"/>
-    </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B315" s="132"/>
+      <c r="C315" s="132"/>
+      <c r="D315" s="133"/>
+      <c r="E315" s="133"/>
+      <c r="F315" s="134"/>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A316" s="92" t="s">
         <v>1</v>
       </c>
@@ -9115,7 +9045,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A317" s="5" t="s">
         <v>6</v>
       </c>
@@ -9127,7 +9057,7 @@
       <c r="E317" s="21"/>
       <c r="F317" s="6"/>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A318" s="20" t="s">
         <v>366</v>
       </c>
@@ -9137,7 +9067,7 @@
       <c r="E318" s="90"/>
       <c r="F318" s="16"/>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A319" s="20" t="s">
         <v>367</v>
       </c>
@@ -9157,7 +9087,7 @@
       </c>
       <c r="F319" s="16"/>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A320" s="20" t="s">
         <v>368</v>
       </c>
@@ -9177,7 +9107,7 @@
       </c>
       <c r="F320" s="16"/>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A321" s="20" t="s">
         <v>369</v>
       </c>
@@ -9197,7 +9127,7 @@
       </c>
       <c r="F321" s="16"/>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A322" s="20" t="s">
         <v>370</v>
       </c>
@@ -9217,7 +9147,7 @@
       </c>
       <c r="F322" s="16"/>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A323" s="20" t="s">
         <v>371</v>
       </c>
@@ -9237,7 +9167,7 @@
       </c>
       <c r="F323" s="16"/>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A324" s="20" t="s">
         <v>372</v>
       </c>
@@ -9249,7 +9179,7 @@
       <c r="E324" s="90"/>
       <c r="F324" s="16"/>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A325" s="20" t="s">
         <v>373</v>
       </c>
@@ -9259,7 +9189,7 @@
       <c r="E325" s="90"/>
       <c r="F325" s="16"/>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A326" s="20" t="s">
         <v>374</v>
       </c>
@@ -9279,7 +9209,7 @@
       </c>
       <c r="F326" s="16"/>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A327" s="20" t="s">
         <v>375</v>
       </c>
@@ -9299,7 +9229,7 @@
       </c>
       <c r="F327" s="16"/>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A328" s="20" t="s">
         <v>376</v>
       </c>
@@ -9319,7 +9249,7 @@
       </c>
       <c r="F328" s="6"/>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A329" s="20" t="s">
         <v>377</v>
       </c>
@@ -9339,7 +9269,7 @@
       </c>
       <c r="F329" s="16"/>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A330" s="20" t="s">
         <v>378</v>
       </c>
@@ -9359,7 +9289,7 @@
       </c>
       <c r="F330" s="16"/>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A331" s="20" t="s">
         <v>379</v>
       </c>
@@ -9379,7 +9309,7 @@
       </c>
       <c r="F331" s="6"/>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A332" s="20" t="s">
         <v>380</v>
       </c>
@@ -9399,7 +9329,7 @@
       </c>
       <c r="F332" s="6"/>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A333" s="20" t="s">
         <v>381</v>
       </c>
@@ -9411,7 +9341,7 @@
       <c r="E333" s="90"/>
       <c r="F333" s="6"/>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A334" s="20" t="s">
         <v>382</v>
       </c>
@@ -9421,7 +9351,7 @@
       <c r="E334" s="90"/>
       <c r="F334" s="6"/>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A335" s="20" t="s">
         <v>269</v>
       </c>
@@ -9441,7 +9371,7 @@
       </c>
       <c r="F335" s="6"/>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A336" s="20" t="s">
         <v>383</v>
       </c>
@@ -9461,7 +9391,7 @@
       </c>
       <c r="F336" s="6"/>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A337" s="20" t="s">
         <v>384</v>
       </c>
@@ -9481,7 +9411,7 @@
       </c>
       <c r="F337" s="6"/>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A338" s="20" t="s">
         <v>385</v>
       </c>
@@ -9501,7 +9431,7 @@
       </c>
       <c r="F338" s="6"/>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A339" s="20" t="s">
         <v>386</v>
       </c>
@@ -9521,7 +9451,7 @@
       </c>
       <c r="F339" s="6"/>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A340" s="20" t="s">
         <v>271</v>
       </c>
@@ -9541,7 +9471,7 @@
       </c>
       <c r="F340" s="6"/>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A341" s="20" t="s">
         <v>387</v>
       </c>
@@ -9553,7 +9483,7 @@
       <c r="E341" s="90"/>
       <c r="F341" s="6"/>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A342" s="20" t="s">
         <v>388</v>
       </c>
@@ -9563,7 +9493,7 @@
       <c r="E342" s="90"/>
       <c r="F342" s="6"/>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A343" s="20" t="s">
         <v>389</v>
       </c>
@@ -9583,7 +9513,7 @@
       </c>
       <c r="F343" s="6"/>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A344" s="20" t="s">
         <v>390</v>
       </c>
@@ -9593,7 +9523,7 @@
       <c r="E344" s="90"/>
       <c r="F344" s="6"/>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A345" s="20" t="s">
         <v>278</v>
       </c>
@@ -9613,7 +9543,7 @@
       </c>
       <c r="F345" s="6"/>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A346" s="20" t="s">
         <v>279</v>
       </c>
@@ -9633,7 +9563,7 @@
       </c>
       <c r="F346" s="6"/>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A347" s="20" t="s">
         <v>391</v>
       </c>
@@ -9653,7 +9583,7 @@
       </c>
       <c r="F347" s="6"/>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A348" s="20" t="s">
         <v>392</v>
       </c>
@@ -9673,7 +9603,7 @@
       </c>
       <c r="F348" s="6"/>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A349" s="20" t="s">
         <v>281</v>
       </c>
@@ -9693,7 +9623,7 @@
       </c>
       <c r="F349" s="6"/>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A350" s="20" t="s">
         <v>393</v>
       </c>
@@ -9713,7 +9643,7 @@
       </c>
       <c r="F350" s="6"/>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A351" s="20" t="s">
         <v>394</v>
       </c>
@@ -9733,7 +9663,7 @@
       </c>
       <c r="F351" s="6"/>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A352" s="20" t="s">
         <v>395</v>
       </c>
@@ -9753,7 +9683,7 @@
       </c>
       <c r="F352" s="6"/>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A353" s="20" t="s">
         <v>396</v>
       </c>
@@ -9773,7 +9703,7 @@
       </c>
       <c r="F353" s="6"/>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A354" s="20" t="s">
         <v>397</v>
       </c>
@@ -9785,7 +9715,7 @@
       <c r="E354" s="90"/>
       <c r="F354" s="6"/>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A355" s="20" t="s">
         <v>398</v>
       </c>
@@ -9795,7 +9725,7 @@
       <c r="E355" s="90"/>
       <c r="F355" s="6"/>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A356" s="20" t="s">
         <v>399</v>
       </c>
@@ -9815,7 +9745,7 @@
       </c>
       <c r="F356" s="6"/>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A357" s="20" t="s">
         <v>400</v>
       </c>
@@ -9835,7 +9765,7 @@
       </c>
       <c r="F357" s="6"/>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A358" s="20" t="s">
         <v>401</v>
       </c>
@@ -9855,7 +9785,7 @@
       </c>
       <c r="F358" s="6"/>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A359" s="20" t="s">
         <v>402</v>
       </c>
@@ -9875,7 +9805,7 @@
       </c>
       <c r="F359" s="6"/>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A360" s="20" t="s">
         <v>403</v>
       </c>
@@ -9887,7 +9817,7 @@
       <c r="E360" s="90"/>
       <c r="F360" s="6"/>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A361" s="20" t="s">
         <v>404</v>
       </c>
@@ -9907,7 +9837,7 @@
       </c>
       <c r="F361" s="6"/>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A362" s="20" t="s">
         <v>405</v>
       </c>
@@ -9919,7 +9849,7 @@
       <c r="E362" s="90"/>
       <c r="F362" s="6"/>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A363" s="20" t="s">
         <v>285</v>
       </c>
@@ -9939,7 +9869,7 @@
       </c>
       <c r="F363" s="6"/>
     </row>
-    <row r="364" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A364" s="67" t="s">
         <v>406</v>
       </c>
@@ -9951,7 +9881,7 @@
       <c r="E364" s="95"/>
       <c r="F364" s="72"/>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A365" s="11" t="s">
         <v>8</v>
       </c>
@@ -9961,7 +9891,7 @@
       <c r="E365" s="60"/>
       <c r="F365" s="14"/>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A366" s="20" t="s">
         <v>65</v>
       </c>
@@ -9971,7 +9901,7 @@
       <c r="E366" s="21"/>
       <c r="F366" s="6"/>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A367" s="20" t="s">
         <v>408</v>
       </c>
@@ -9991,7 +9921,7 @@
       </c>
       <c r="F367" s="6"/>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A368" s="20" t="s">
         <v>409</v>
       </c>
@@ -10011,7 +9941,7 @@
       </c>
       <c r="F368" s="6"/>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A369" s="20" t="s">
         <v>410</v>
       </c>
@@ -10031,7 +9961,7 @@
       </c>
       <c r="F369" s="6"/>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A370" s="20" t="s">
         <v>271</v>
       </c>
@@ -10051,7 +9981,7 @@
       </c>
       <c r="F370" s="6"/>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A371" s="20" t="s">
         <v>411</v>
       </c>
@@ -10063,7 +9993,7 @@
       <c r="E371" s="21"/>
       <c r="F371" s="6"/>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A372" s="20" t="s">
         <v>105</v>
       </c>
@@ -10073,7 +10003,7 @@
       <c r="E372" s="21"/>
       <c r="F372" s="6"/>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A373" s="20" t="s">
         <v>412</v>
       </c>
@@ -10093,7 +10023,7 @@
       </c>
       <c r="F373" s="6"/>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A374" s="20" t="s">
         <v>413</v>
       </c>
@@ -10113,7 +10043,7 @@
       </c>
       <c r="F374" s="6"/>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A375" s="20" t="s">
         <v>414</v>
       </c>
@@ -10133,7 +10063,7 @@
       </c>
       <c r="F375" s="6"/>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A376" s="20" t="s">
         <v>415</v>
       </c>
@@ -10153,7 +10083,7 @@
       </c>
       <c r="F376" s="6"/>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A377" s="20" t="s">
         <v>416</v>
       </c>
@@ -10173,7 +10103,7 @@
       </c>
       <c r="F377" s="6"/>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A378" s="20" t="s">
         <v>417</v>
       </c>
@@ -10185,7 +10115,7 @@
       <c r="E378" s="21"/>
       <c r="F378" s="6"/>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A379" s="20" t="s">
         <v>405</v>
       </c>
@@ -10197,7 +10127,7 @@
       <c r="E379" s="21"/>
       <c r="F379" s="6"/>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A380" s="20" t="s">
         <v>285</v>
       </c>
@@ -10217,7 +10147,7 @@
       </c>
       <c r="F380" s="6"/>
     </row>
-    <row r="381" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:6" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A381" s="24" t="s">
         <v>418</v>
       </c>
@@ -10245,6 +10175,7 @@
     <mergeCell ref="A145:F145"/>
     <mergeCell ref="A164:F164"/>
   </mergeCells>
+  <phoneticPr fontId="18" type="noConversion"/>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" errorTitle="Expenditures" error="Expenditures must be a number that is greater than or equal to zero." sqref="B17" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>0</formula1>
@@ -10322,14 +10253,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A72D1499-D3A0-4266-A574-149D619EFB6A}">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:W24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="16" max="16" width="21.140625" customWidth="1"/>
+    <col min="16" max="16" width="21.1640625" customWidth="1"/>
     <col min="20" max="20" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A1" s="115" t="s">
         <v>0</v>
       </c>
@@ -10356,7 +10288,7 @@
       <c r="V1" s="116"/>
       <c r="W1" s="116"/>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.45">
       <c r="T3" s="120" t="s">
         <v>468</v>
       </c>
@@ -10366,7 +10298,7 @@
         <v>1.0000000000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.45">
       <c r="Q4" t="s">
         <v>466</v>
       </c>
@@ -10374,7 +10306,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.45">
       <c r="P5" s="71" t="s">
         <v>451</v>
       </c>
@@ -10393,7 +10325,7 @@
         <v>0.39285714285714285</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.45">
       <c r="P6" s="71" t="s">
         <v>452</v>
       </c>
@@ -10412,7 +10344,7 @@
         <v>4.7619047619047616E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.45">
       <c r="P7" s="71" t="s">
         <v>453</v>
       </c>
@@ -10431,7 +10363,7 @@
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.45">
       <c r="P8" t="s">
         <v>454</v>
       </c>
@@ -10447,7 +10379,7 @@
         <v>0.14285714285714285</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.45">
       <c r="P9" t="s">
         <v>455</v>
       </c>
@@ -10463,7 +10395,7 @@
         <v>0.13095238095238096</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.45">
       <c r="P10" t="s">
         <v>456</v>
       </c>
@@ -10479,7 +10411,7 @@
         <v>5.9523809523809521E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.45">
       <c r="P11" s="71" t="s">
         <v>457</v>
       </c>
@@ -10498,7 +10430,7 @@
         <v>4.7619047619047616E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.45">
       <c r="P12" s="71" t="s">
         <v>458</v>
       </c>
@@ -10517,7 +10449,7 @@
         <v>2.3809523809523808E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.45">
       <c r="P13" s="71" t="s">
         <v>459</v>
       </c>
@@ -10536,7 +10468,7 @@
         <v>2.3809523809523808E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.45">
       <c r="P14" s="71" t="s">
         <v>460</v>
       </c>
@@ -10555,7 +10487,7 @@
         <v>4.7619047619047616E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.45">
       <c r="P15" s="71" t="s">
         <v>461</v>
       </c>
@@ -10569,7 +10501,7 @@
       <c r="T15" s="123"/>
       <c r="U15" s="124"/>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.45">
       <c r="P16" t="s">
         <v>462</v>
       </c>
@@ -10580,7 +10512,7 @@
       <c r="T16" s="122"/>
       <c r="U16" s="125"/>
     </row>
-    <row r="17" spans="16:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="16:21" x14ac:dyDescent="0.45">
       <c r="P17" s="71" t="s">
         <v>463</v>
       </c>
@@ -10594,7 +10526,7 @@
       <c r="T17" s="122"/>
       <c r="U17" s="125"/>
     </row>
-    <row r="18" spans="16:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="16:21" x14ac:dyDescent="0.45">
       <c r="P18" t="s">
         <v>464</v>
       </c>
@@ -10603,7 +10535,7 @@
       </c>
       <c r="R18" s="112"/>
     </row>
-    <row r="19" spans="16:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="16:21" x14ac:dyDescent="0.45">
       <c r="P19" s="71" t="s">
         <v>465</v>
       </c>
@@ -10615,18 +10547,18 @@
         <v>0.39285714285714285</v>
       </c>
     </row>
-    <row r="20" spans="16:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="16:21" x14ac:dyDescent="0.45">
       <c r="Q20" s="71">
         <f>SUM(Q5:Q7,Q11:Q15,Q17,Q19)</f>
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="16:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="16:21" x14ac:dyDescent="0.45">
       <c r="P22" s="71" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="23" spans="16:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="16:21" x14ac:dyDescent="0.45">
       <c r="P23" t="s">
         <v>257</v>
       </c>
@@ -10638,7 +10570,7 @@
         <v>0.53533333333333433</v>
       </c>
     </row>
-    <row r="24" spans="16:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="16:21" x14ac:dyDescent="0.45">
       <c r="P24" t="s">
         <v>258</v>
       </c>
@@ -10651,6 +10583,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -10659,29 +10592,30 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9EEF34C-533F-4D76-B456-E79BEA524DCC}">
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:AQ101"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="26.140625" customWidth="1"/>
-    <col min="2" max="2" width="25.42578125" customWidth="1"/>
+    <col min="1" max="1" width="26.1640625" customWidth="1"/>
+    <col min="2" max="2" width="25.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.45">
       <c r="B5">
         <v>2021</v>
       </c>
@@ -10773,7 +10707,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>199</v>
       </c>
@@ -10868,7 +10802,7 @@
         <v>1213309.5172925084</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>470</v>
       </c>
@@ -10963,7 +10897,7 @@
         <v>546510.48924034019</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>205</v>
       </c>
@@ -11058,7 +10992,7 @@
         <v>2090069.7248419826</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>209</v>
       </c>
@@ -11153,12 +11087,12 @@
         <v>1406155.6987444595</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.45">
       <c r="B12">
         <v>2021</v>
       </c>
@@ -11250,7 +11184,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>199</v>
       </c>
@@ -11345,7 +11279,7 @@
         <v>2392614.7852066685</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>470</v>
       </c>
@@ -11440,7 +11374,7 @@
         <v>834725.65369765111</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>205</v>
       </c>
@@ -11535,7 +11469,7 @@
         <v>7911207.6996868448</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>209</v>
       </c>
@@ -11630,17 +11564,17 @@
         <v>2772902.4351726989</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.45">
       <c r="B19">
         <v>2021</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>199</v>
       </c>
@@ -11677,7 +11611,7 @@
       <c r="AD20" s="124"/>
       <c r="AE20" s="124"/>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>470</v>
       </c>
@@ -11714,7 +11648,7 @@
       <c r="AD21" s="124"/>
       <c r="AE21" s="124"/>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>205</v>
       </c>
@@ -11751,7 +11685,7 @@
       <c r="AD22" s="124"/>
       <c r="AE22" s="124"/>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>209</v>
       </c>
@@ -11788,17 +11722,17 @@
       <c r="AD23" s="124"/>
       <c r="AE23" s="124"/>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.45">
       <c r="B26">
         <v>2021</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>199</v>
       </c>
@@ -11806,7 +11740,7 @@
         <v>65750.800457615216</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>470</v>
       </c>
@@ -11814,7 +11748,7 @@
         <v>26096.967191940064</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>205</v>
       </c>
@@ -11822,7 +11756,7 @@
         <v>133213.1552570395</v>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>209</v>
       </c>
@@ -11830,17 +11764,17 @@
         <v>65750.800457615216</v>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.45">
       <c r="B33">
         <v>2021</v>
       </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>199</v>
       </c>
@@ -11877,7 +11811,7 @@
       <c r="AD34" s="124"/>
       <c r="AE34" s="124"/>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>470</v>
       </c>
@@ -11914,7 +11848,7 @@
       <c r="AD35" s="124"/>
       <c r="AE35" s="124"/>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>205</v>
       </c>
@@ -11951,7 +11885,7 @@
       <c r="AD36" s="124"/>
       <c r="AE36" s="124"/>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>209</v>
       </c>
@@ -11988,61 +11922,57 @@
       <c r="AD37" s="124"/>
       <c r="AE37" s="124"/>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:31" x14ac:dyDescent="0.45">
       <c r="B40">
         <v>2021</v>
       </c>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>199</v>
       </c>
       <c r="B41" s="124">
-        <f>'[1]CCaMC-VOaMCpUC'!$EB$2</f>
         <v>7.1681929364874337</v>
       </c>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>470</v>
       </c>
       <c r="B42" s="124">
-        <f>'[1]CCaMC-VOaMCpUC'!$EB$4</f>
         <v>1.6607160940325494</v>
       </c>
     </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>205</v>
       </c>
       <c r="B43" s="124">
-        <f>'[1]CCaMC-VOaMCpUC'!$EB$10</f>
         <v>4.2704128132265557</v>
       </c>
     </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>209</v>
       </c>
       <c r="B44" s="124">
-        <f>'[1]CCaMC-VOaMCpUC'!$EB$14</f>
         <v>12.14376215122577</v>
       </c>
     </row>
-    <row r="45" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:31" x14ac:dyDescent="0.45">
       <c r="B45" s="124"/>
     </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="47" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:31" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
         <v>487</v>
       </c>
@@ -12050,7 +11980,7 @@
         <v>91.94</v>
       </c>
     </row>
-    <row r="48" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:31" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
         <v>488</v>
       </c>
@@ -12058,7 +11988,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:43" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
         <v>489</v>
       </c>
@@ -12066,12 +11996,12 @@
         <v>48.75</v>
       </c>
     </row>
-    <row r="50" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="51" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:43" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
         <v>491</v>
       </c>
@@ -12082,7 +12012,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="52" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:43" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
         <v>492</v>
       </c>
@@ -12093,7 +12023,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="53" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:43" x14ac:dyDescent="0.45">
       <c r="B53" t="s">
         <v>493</v>
       </c>
@@ -12104,7 +12034,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="54" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:43" x14ac:dyDescent="0.45">
       <c r="B54" t="s">
         <v>494</v>
       </c>
@@ -12115,7 +12045,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="55" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:43" x14ac:dyDescent="0.45">
       <c r="B55" t="s">
         <v>65</v>
       </c>
@@ -12126,12 +12056,12 @@
         <v>500</v>
       </c>
     </row>
-    <row r="58" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="59" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A59" s="126"/>
       <c r="B59" s="110" t="s">
         <v>163</v>
@@ -12260,7 +12190,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="60" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>199</v>
       </c>
@@ -12433,7 +12363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>470</v>
       </c>
@@ -12606,7 +12536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>205</v>
       </c>
@@ -12779,7 +12709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>209</v>
       </c>
@@ -12952,20 +12882,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:43" x14ac:dyDescent="0.45">
       <c r="B64" s="128"/>
     </row>
-    <row r="65" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="66" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="67" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A67" s="126"/>
       <c r="B67" s="110" t="s">
         <v>163</v>
@@ -13094,7 +13024,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="68" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>199</v>
       </c>
@@ -13147,7 +13077,7 @@
       <c r="AP68" s="129"/>
       <c r="AQ68" s="129"/>
     </row>
-    <row r="69" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>470</v>
       </c>
@@ -13200,7 +13130,7 @@
       <c r="AP69" s="129"/>
       <c r="AQ69" s="129"/>
     </row>
-    <row r="70" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>205</v>
       </c>
@@ -13253,7 +13183,7 @@
       <c r="AP70" s="129"/>
       <c r="AQ70" s="129"/>
     </row>
-    <row r="71" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>209</v>
       </c>
@@ -13306,12 +13236,12 @@
       <c r="AP71" s="129"/>
       <c r="AQ71" s="129"/>
     </row>
-    <row r="73" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="74" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A74" s="126"/>
       <c r="B74" s="110" t="s">
         <v>163</v>
@@ -13440,7 +13370,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="75" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>199</v>
       </c>
@@ -13613,7 +13543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>470</v>
       </c>
@@ -13786,7 +13716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>205</v>
       </c>
@@ -13959,7 +13889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>209</v>
       </c>
@@ -14132,7 +14062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:43" x14ac:dyDescent="0.45">
       <c r="B79" s="128"/>
       <c r="C79" s="128"/>
       <c r="D79" s="128"/>
@@ -14176,17 +14106,17 @@
       <c r="AP79" s="128"/>
       <c r="AQ79" s="128"/>
     </row>
-    <row r="80" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="81" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="82" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A82" s="126"/>
       <c r="B82" s="110" t="s">
         <v>163</v>
@@ -14315,7 +14245,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="83" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>199</v>
       </c>
@@ -14365,7 +14295,7 @@
       <c r="AP83" s="129"/>
       <c r="AQ83" s="129"/>
     </row>
-    <row r="84" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>470</v>
       </c>
@@ -14415,7 +14345,7 @@
       <c r="AP84" s="129"/>
       <c r="AQ84" s="129"/>
     </row>
-    <row r="85" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>205</v>
       </c>
@@ -14465,7 +14395,7 @@
       <c r="AP85" s="129"/>
       <c r="AQ85" s="129"/>
     </row>
-    <row r="86" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>209</v>
       </c>
@@ -14515,12 +14445,12 @@
       <c r="AP86" s="129"/>
       <c r="AQ86" s="129"/>
     </row>
-    <row r="88" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="89" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A89" s="126"/>
       <c r="B89" s="110" t="s">
         <v>163</v>
@@ -14649,7 +14579,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="90" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>199</v>
       </c>
@@ -14822,7 +14752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>470</v>
       </c>
@@ -14995,7 +14925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>205</v>
       </c>
@@ -15168,7 +15098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>209</v>
       </c>
@@ -15341,20 +15271,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:43" x14ac:dyDescent="0.45">
       <c r="B94" s="128"/>
     </row>
-    <row r="95" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="96" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="97" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A97" s="126"/>
       <c r="B97" s="110" t="s">
         <v>163</v>
@@ -15483,7 +15413,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="98" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>199</v>
       </c>
@@ -15533,7 +15463,7 @@
       <c r="AP98" s="129"/>
       <c r="AQ98" s="129"/>
     </row>
-    <row r="99" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>470</v>
       </c>
@@ -15583,7 +15513,7 @@
       <c r="AP99" s="129"/>
       <c r="AQ99" s="129"/>
     </row>
-    <row r="100" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>205</v>
       </c>
@@ -15633,7 +15563,7 @@
       <c r="AP100" s="129"/>
       <c r="AQ100" s="129"/>
     </row>
-    <row r="101" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>209</v>
       </c>
@@ -15684,43 +15614,44 @@
       <c r="AQ101" s="129"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet6">
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:AS25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="26.5703125" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.7109375" customWidth="1"/>
-    <col min="14" max="24" width="7.7109375" customWidth="1"/>
-    <col min="25" max="26" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="9.7109375" customWidth="1"/>
-    <col min="29" max="33" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="41" max="43" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.58203125" customWidth="1"/>
+    <col min="2" max="2" width="10.58203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.75" customWidth="1"/>
+    <col min="5" max="5" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.75" customWidth="1"/>
+    <col min="14" max="24" width="7.75" customWidth="1"/>
+    <col min="25" max="26" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="9.75" customWidth="1"/>
+    <col min="29" max="33" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="41" max="43" width="9.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A1" s="126" t="s">
         <v>471</v>
       </c>
@@ -15851,7 +15782,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>199</v>
       </c>
@@ -16024,7 +15955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>469</v>
       </c>
@@ -16197,7 +16128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>470</v>
       </c>
@@ -16370,7 +16301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>200</v>
       </c>
@@ -16543,7 +16474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>201</v>
       </c>
@@ -16716,7 +16647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>202</v>
       </c>
@@ -16889,7 +16820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>203</v>
       </c>
@@ -17062,7 +16993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>204</v>
       </c>
@@ -17235,7 +17166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>205</v>
       </c>
@@ -17408,7 +17339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>206</v>
       </c>
@@ -17581,7 +17512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>207</v>
       </c>
@@ -17754,7 +17685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>208</v>
       </c>
@@ -17927,7 +17858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>209</v>
       </c>
@@ -18100,7 +18031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>210</v>
       </c>
@@ -18273,7 +18204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>211</v>
       </c>
@@ -18446,7 +18377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:45" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>212</v>
       </c>
@@ -18619,7 +18550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:45" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>213</v>
       </c>
@@ -18792,7 +18723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:45" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>472</v>
       </c>
@@ -18966,7 +18897,7 @@
       </c>
       <c r="AS19" s="77"/>
     </row>
-    <row r="20" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:45" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>473</v>
       </c>
@@ -19140,7 +19071,7 @@
       </c>
       <c r="AS20" s="77"/>
     </row>
-    <row r="21" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:45" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>474</v>
       </c>
@@ -19314,7 +19245,7 @@
       </c>
       <c r="AS21" s="77"/>
     </row>
-    <row r="22" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:45" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>475</v>
       </c>
@@ -19488,7 +19419,7 @@
       </c>
       <c r="AS22" s="77"/>
     </row>
-    <row r="23" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:45" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>476</v>
       </c>
@@ -19661,8 +19592,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A24" s="138" t="s">
+    <row r="24" spans="1:45" x14ac:dyDescent="0.45">
+      <c r="A24" s="130" t="s">
         <v>511</v>
       </c>
       <c r="B24" s="77">
@@ -19834,8 +19765,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A25" s="138" t="s">
+    <row r="25" spans="1:45" x14ac:dyDescent="0.45">
+      <c r="A25" s="130" t="s">
         <v>512</v>
       </c>
       <c r="B25" s="77">
@@ -20008,6 +19939,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -20015,36 +19947,36 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet7">
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:AQ25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.140625" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.4140625" customWidth="1"/>
+    <col min="2" max="2" width="10.58203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.75" customWidth="1"/>
+    <col min="5" max="5" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.1640625" customWidth="1"/>
+    <col min="12" max="12" width="9.75" bestFit="1" customWidth="1"/>
     <col min="13" max="24" width="8" customWidth="1"/>
-    <col min="25" max="26" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="9.7109375" customWidth="1"/>
-    <col min="29" max="33" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="7.140625" customWidth="1"/>
-    <col min="41" max="43" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="9.75" customWidth="1"/>
+    <col min="29" max="33" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="7.1640625" customWidth="1"/>
+    <col min="41" max="43" width="9.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A1" s="127" t="s">
         <v>471</v>
       </c>
@@ -20175,7 +20107,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>199</v>
       </c>
@@ -20348,7 +20280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>469</v>
       </c>
@@ -20521,7 +20453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>470</v>
       </c>
@@ -20694,7 +20626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>200</v>
       </c>
@@ -20867,7 +20799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>201</v>
       </c>
@@ -21040,7 +20972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>202</v>
       </c>
@@ -21213,7 +21145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>203</v>
       </c>
@@ -21386,7 +21318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>204</v>
       </c>
@@ -21559,7 +21491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>205</v>
       </c>
@@ -21732,7 +21664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>206</v>
       </c>
@@ -21905,7 +21837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>207</v>
       </c>
@@ -22078,7 +22010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>208</v>
       </c>
@@ -22251,7 +22183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>209</v>
       </c>
@@ -22424,7 +22356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>210</v>
       </c>
@@ -22597,7 +22529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>211</v>
       </c>
@@ -22770,7 +22702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>212</v>
       </c>
@@ -22943,7 +22875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>213</v>
       </c>
@@ -23116,7 +23048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>472</v>
       </c>
@@ -23289,7 +23221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>473</v>
       </c>
@@ -23462,7 +23394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>474</v>
       </c>
@@ -23635,7 +23567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>475</v>
       </c>
@@ -23808,7 +23740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>476</v>
       </c>
@@ -23981,8 +23913,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A24" s="138" t="s">
+    <row r="24" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A24" s="130" t="s">
         <v>511</v>
       </c>
       <c r="B24" s="77">
@@ -24154,8 +24086,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A25" s="138" t="s">
+    <row r="25" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A25" s="130" t="s">
         <v>512</v>
       </c>
       <c r="B25" s="77">
@@ -24328,42 +24260,43 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet8">
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:AQ25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="24" width="8.28515625" customWidth="1"/>
-    <col min="25" max="26" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="9.7109375" customWidth="1"/>
-    <col min="29" max="33" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="41" max="43" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.4140625" customWidth="1"/>
+    <col min="2" max="2" width="10.58203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.75" customWidth="1"/>
+    <col min="5" max="5" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="13" max="24" width="8.25" customWidth="1"/>
+    <col min="25" max="26" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="9.75" customWidth="1"/>
+    <col min="29" max="33" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="41" max="43" width="9.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A1" s="127" t="s">
         <v>471</v>
       </c>
@@ -24494,7 +24427,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>199</v>
       </c>
@@ -24667,7 +24600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>469</v>
       </c>
@@ -24840,7 +24773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>470</v>
       </c>
@@ -25013,7 +24946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>200</v>
       </c>
@@ -25186,7 +25119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>201</v>
       </c>
@@ -25359,7 +25292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>202</v>
       </c>
@@ -25490,7 +25423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>203</v>
       </c>
@@ -25621,7 +25554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>204</v>
       </c>
@@ -25752,7 +25685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>205</v>
       </c>
@@ -25925,7 +25858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>206</v>
       </c>
@@ -26098,7 +26031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>207</v>
       </c>
@@ -26271,7 +26204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>208</v>
       </c>
@@ -26444,7 +26377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>209</v>
       </c>
@@ -26617,7 +26550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>210</v>
       </c>
@@ -26748,7 +26681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>211</v>
       </c>
@@ -26921,7 +26854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>212</v>
       </c>
@@ -27094,7 +27027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>213</v>
       </c>
@@ -27267,7 +27200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>472</v>
       </c>
@@ -27440,7 +27373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>473</v>
       </c>
@@ -27613,7 +27546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>474</v>
       </c>
@@ -27786,7 +27719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>475</v>
       </c>
@@ -27959,7 +27892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>476</v>
       </c>
@@ -28132,8 +28065,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A24" s="138" t="s">
+    <row r="24" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A24" s="130" t="s">
         <v>511</v>
       </c>
       <c r="B24" s="77">
@@ -28305,8 +28238,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A25" s="138" t="s">
+    <row r="25" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="A25" s="130" t="s">
         <v>512</v>
       </c>
       <c r="B25" s="77">
@@ -28479,6 +28412,178 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A58D59A-482F-4C63-BF4F-164BA0A4E0EA}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51DBD24E-E913-4055-9E6A-DAC50E5C13D4}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB340F9B-30B2-4E8D-9C66-00F6FB26E224}"/>
 </file>